--- a/accounts-receivable/cash-application-tracker/Cash_Application_Tracker_2026-06.xlsx
+++ b/accounts-receivable/cash-application-tracker/Cash_Application_Tracker_2026-06.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rab35ba07b3be45b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Register" sheetId="2" r:id="R9de381b9e8914a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Receipts" sheetId="3" r:id="Rfceae096bbe8484c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application Detail" sheetId="4" r:id="R4b846dccfe124fdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Summary" sheetId="5" r:id="Rcfb5650862fe42e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Checks" sheetId="6" r:id="Rd682463a45de445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Reea30bd7fbfc4453"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Register" sheetId="2" r:id="R67484bb0b5e648a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Receipts" sheetId="3" r:id="R38ff20843de4421c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application Detail" sheetId="4" r:id="R935845a89a134791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Summary" sheetId="5" r:id="Rd6a99ec09bac48a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Checks" sheetId="6" r:id="R35c314027bd543ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1746,7 +1746,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -1757,7 +1757,7 @@
         <x:color rgb="FF8A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4E5"/>
         </x:patternFill>
       </x:fill>
@@ -1768,7 +1768,7 @@
         <x:color rgb="FF8A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4E5"/>
         </x:patternFill>
       </x:fill>
@@ -1779,7 +1779,7 @@
         <x:color rgb="FFC63D3D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1790,7 +1790,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -1801,7 +1801,7 @@
         <x:color rgb="FF8A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4E5"/>
         </x:patternFill>
       </x:fill>
@@ -1812,7 +1812,7 @@
         <x:color rgb="FFC63D3D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1823,7 +1823,7 @@
         <x:color rgb="FFC63D3D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1833,7 +1833,7 @@
         <x:color rgb="FF8A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4E5"/>
         </x:patternFill>
       </x:fill>
@@ -1844,7 +1844,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -1855,7 +1855,7 @@
         <x:color rgb="FFC63D3D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1866,7 +1866,7 @@
         <x:color rgb="FFC63D3D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1877,7 +1877,7 @@
         <x:color rgb="FFC63D3D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1888,7 +1888,7 @@
         <x:color rgb="FF8A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4E5"/>
         </x:patternFill>
       </x:fill>
@@ -1899,7 +1899,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -1910,7 +1910,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -1921,7 +1921,7 @@
         <x:color rgb="FFC63D3D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -2246,7 +2246,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rccfe4f8520b34ca6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R94a64e411ff142dc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2276,7 +2276,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78c872b1019b4805"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5901db173f104a42"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2756,7 +2756,7 @@
         <x:v>Portfolio owner</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>SanDAce07</x:v>
+        <x:v>Sandesh Lama Tamang</x:v>
       </x:c>
       <x:c r="H4" s="10"/>
       <x:c r="I4" s="12" t="str">
@@ -3328,8 +3328,8 @@
     <x:mergeCell ref="J35:O38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0bfaaa3b85e427e"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20a834ff65634807"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9880ca1786234b4d"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73602de3361f475a"/>
 </x:worksheet>
 </file>
 
@@ -4503,7 +4503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae042765632745c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39e2150665de4a98"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6062,7 +6062,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc450c09bc24445b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R911f5ccdb6814c16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7557,7 +7557,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35c8b9a3c33149e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca55a2d8fff04069"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8409,7 +8409,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05828463068e4b90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8325380b5c34d64"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
